--- a/基金趋势分析.xlsx
+++ b/基金趋势分析.xlsx
@@ -501,44 +501,44 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>501046</t>
+          <t>014916</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>财通多策略福鑫定开混合</t>
+          <t>财通匠心优选一年持有混合C</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>9.2552</v>
+        <v>2.9685</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-2.31%</t>
+          <t>-1.89%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>+12.64%</t>
+          <t>+12.19%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>+42.13%</t>
+          <t>+40.11%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>9.474500000000001</v>
+        <v>3.0256</v>
       </c>
       <c r="I2" t="n">
-        <v>8.575699999999999</v>
+        <v>2.7542</v>
       </c>
       <c r="J2" t="n">
-        <v>7.0617</v>
+        <v>2.2911</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>+31.06%</t>
+          <t>+29.57%</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -558,44 +558,44 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>501225</t>
+          <t>021528</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>景顺长城全球半导体芯片股票A(QDII-LOF)(人民币)</t>
+          <t>财通成长优选混合C</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>3.2876</v>
+        <v>4.336</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>+0.27%</t>
+          <t>-2.12%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>+5.98%</t>
+          <t>+9.11%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>+21.49%</t>
+          <t>+35.33%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>3.3193</v>
+        <v>4.43</v>
       </c>
       <c r="I3" t="n">
-        <v>3.1613</v>
+        <v>4.117</v>
       </c>
       <c r="J3" t="n">
-        <v>2.8801</v>
+        <v>3.461</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>+14.15%</t>
+          <t>+25.28%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
